--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -1026,67 +1026,67 @@
         <v>0.59</v>
       </c>
       <c r="C16">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="D16">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="E16">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="F16">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="G16">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H16">
-        <v>0.6</v>
+        <v>0.56</v>
       </c>
       <c r="I16">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="J16">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="K16">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="L16">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="M16">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="N16">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="O16">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="P16">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="Q16">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="R16">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="S16">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="T16">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="U16">
         <v>0.28</v>
       </c>
       <c r="V16">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="X16">
         <v>0.29</v>
